--- a/捕鱼游戏数学-PartIV-可调参数模型.xlsx
+++ b/捕鱼游戏数学-PartIV-可调参数模型.xlsx
@@ -1577,6 +1577,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:V53" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -2324,5 +2327,8 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:R49" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/捕鱼游戏数学-PartIV-可调参数模型.xlsx
+++ b/捕鱼游戏数学-PartIV-可调参数模型.xlsx
@@ -10,7 +10,7 @@
     <sheet name="说明" sheetId="1" r:id="rId1"/>
     <sheet name="IV 三个可调参数" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -984,7 +984,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1038,6 +1038,22 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1392,167 +1408,167 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="29" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="31" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="30" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="30" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="30" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="30" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="29" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="31" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="30" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="31" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="32" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="30" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="30" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="33" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="32" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="31" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="32" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="31" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="30" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="30" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="31" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="32" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="31" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="32" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="31" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="31" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="34" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="30" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:1">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="35" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="36" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="36" t="s">
         <v>29</v>
       </c>
     </row>
